--- a/jpcore-r4/release/v1.2.0/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
+++ b/jpcore-r4/release/v1.2.0/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
+++ b/jpcore-r4/release/v1.2.0/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
+++ b/jpcore-r4/release/v1.2.0/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>
